--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9255295214</v>
+        <v>46157.93105947684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105947684</v>
+        <v>46157.93131735905</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93131735905</v>
+        <v>46157.93379705276</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93379705276</v>
+        <v>46157.93690176847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93690176847</v>
+        <v>46158.28202981373</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28202981373</v>
+        <v>46158.29733800724</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29733800724</v>
+        <v>46158.29802256558</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29802256558</v>
+        <v>46158.33366703721</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33366703721</v>
+        <v>46158.37218549222</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_19-59-34/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218549222</v>
+        <v>46158.37273559585</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
